--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_educacion.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -792,7 +792,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -946,7 +946,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3337,7 +3337,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6133,7 +6133,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7069,7 +7069,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7385,7 +7385,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8412,7 +8412,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9354,7 +9354,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10144,7 +10144,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10223,7 +10223,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10689,7 +10689,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11155,7 +11155,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11309,7 +11309,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11540,7 +11540,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11617,7 +11617,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11850,7 +11850,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -12008,7 +12008,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12719,7 +12719,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13509,7 +13509,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13588,7 +13588,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13973,7 +13973,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14368,7 +14368,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14526,7 +14526,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14605,7 +14605,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14684,7 +14684,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14921,7 +14921,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -15079,7 +15079,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15474,7 +15474,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15628,7 +15628,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15940,7 +15940,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -16173,7 +16173,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16404,7 +16404,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16481,7 +16481,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16789,7 +16789,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16943,7 +16943,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17180,7 +17180,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17338,7 +17338,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17417,7 +17417,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17494,7 +17494,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17573,7 +17573,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17652,7 +17652,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17810,7 +17810,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18047,7 +18047,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18205,7 +18205,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18363,7 +18363,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18442,7 +18442,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18521,7 +18521,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19064,7 +19064,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19141,7 +19141,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19297,7 +19297,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19611,7 +19611,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19765,7 +19765,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19921,7 +19921,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20308,7 +20308,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20539,7 +20539,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20616,7 +20616,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20924,7 +20924,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21001,7 +21001,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21155,7 +21155,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="P271" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q271" s="4" t="n"/>
@@ -21386,7 +21386,7 @@
       </c>
       <c r="P272" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q272" s="4" t="n"/>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="P273" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q273" s="4" t="n"/>
@@ -21540,7 +21540,7 @@
       </c>
       <c r="P274" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q274" s="4" t="n"/>
@@ -21617,7 +21617,7 @@
       </c>
       <c r="P275" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q275" s="4" t="n"/>
@@ -21694,7 +21694,7 @@
       </c>
       <c r="P276" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q276" s="4" t="n"/>
@@ -21771,7 +21771,7 @@
       </c>
       <c r="P277" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q277" s="4" t="n"/>
@@ -21848,7 +21848,7 @@
       </c>
       <c r="P278" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q278" s="4" t="n"/>
@@ -21925,7 +21925,7 @@
       </c>
       <c r="P279" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q279" s="4" t="n"/>
@@ -22002,7 +22002,7 @@
       </c>
       <c r="P280" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q280" s="4" t="n"/>
@@ -22081,7 +22081,7 @@
       </c>
       <c r="P281" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q281" s="4" t="n"/>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="P282" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q282" s="4" t="n"/>
@@ -22239,7 +22239,7 @@
       </c>
       <c r="P283" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q283" s="4" t="n"/>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="P284" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q284" s="4" t="n"/>
@@ -22395,7 +22395,7 @@
       </c>
       <c r="P285" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q285" s="4" t="n"/>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="P286" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q286" s="4" t="n"/>
@@ -22551,7 +22551,7 @@
       </c>
       <c r="P287" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q287" s="4" t="n"/>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="P288" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q288" s="4" t="n"/>
@@ -22707,7 +22707,7 @@
       </c>
       <c r="P289" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q289" s="4" t="n"/>
@@ -22784,7 +22784,7 @@
       </c>
       <c r="P290" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q290" s="4" t="n"/>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="P291" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q291" s="4" t="n"/>
@@ -22942,7 +22942,7 @@
       </c>
       <c r="P292" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q292" s="4" t="n"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="P293" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q293" s="4" t="n"/>
@@ -23100,7 +23100,7 @@
       </c>
       <c r="P294" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q294" s="4" t="n"/>
@@ -23179,7 +23179,7 @@
       </c>
       <c r="P295" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q295" s="4" t="n"/>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="P296" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q296" s="4" t="n"/>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="P297" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q297" s="4" t="n"/>
@@ -23412,7 +23412,7 @@
       </c>
       <c r="P298" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q298" s="4" t="n"/>
@@ -23491,7 +23491,7 @@
       </c>
       <c r="P299" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q299" s="4" t="n"/>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="P300" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q300" s="4" t="n"/>
@@ -23647,7 +23647,7 @@
       </c>
       <c r="P301" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q301" s="4" t="n"/>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="P302" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q302" s="4" t="n"/>
@@ -23803,7 +23803,7 @@
       </c>
       <c r="P303" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q303" s="4" t="n"/>
@@ -23882,7 +23882,7 @@
       </c>
       <c r="P304" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q304" s="4" t="n"/>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="P305" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q305" s="4" t="n"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="P306" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q306" s="4" t="n"/>
@@ -24115,7 +24115,7 @@
       </c>
       <c r="P307" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q307" s="4" t="n"/>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="P308" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q308" s="4" t="n"/>
@@ -24269,7 +24269,7 @@
       </c>
       <c r="P309" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q309" s="4" t="n"/>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="P310" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q310" s="4" t="n"/>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="P311" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q311" s="4" t="n"/>
@@ -24500,7 +24500,7 @@
       </c>
       <c r="P312" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q312" s="4" t="n"/>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="P313" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q313" s="4" t="n"/>
@@ -24654,7 +24654,7 @@
       </c>
       <c r="P314" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q314" s="4" t="n"/>
@@ -24731,7 +24731,7 @@
       </c>
       <c r="P315" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q315" s="4" t="n"/>
@@ -24808,7 +24808,7 @@
       </c>
       <c r="P316" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q316" s="4" t="n"/>
@@ -24887,7 +24887,7 @@
       </c>
       <c r="P317" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q317" s="4" t="n"/>
@@ -24966,7 +24966,7 @@
       </c>
       <c r="P318" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q318" s="4" t="n"/>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="P319" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q319" s="4" t="n"/>
@@ -25122,7 +25122,7 @@
       </c>
       <c r="P320" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q320" s="4" t="n"/>
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P321" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q321" s="4" t="n"/>
@@ -25276,7 +25276,7 @@
       </c>
       <c r="P322" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q322" s="4" t="n"/>
@@ -25353,7 +25353,7 @@
       </c>
       <c r="P323" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q323" s="4" t="n"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="P324" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q324" s="4" t="n"/>
@@ -25507,7 +25507,7 @@
       </c>
       <c r="P325" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q325" s="4" t="n"/>
@@ -25584,7 +25584,7 @@
       </c>
       <c r="P326" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q326" s="4" t="n"/>
@@ -25661,7 +25661,7 @@
       </c>
       <c r="P327" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q327" s="4" t="n"/>
@@ -25738,7 +25738,7 @@
       </c>
       <c r="P328" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q328" s="4" t="n"/>
@@ -25815,7 +25815,7 @@
       </c>
       <c r="P329" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q329" s="4" t="n"/>
@@ -25892,7 +25892,7 @@
       </c>
       <c r="P330" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q330" s="4" t="n"/>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="P331" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q331" s="4" t="n"/>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="P332" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q332" s="4" t="n"/>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="P333" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q333" s="4" t="n"/>
@@ -26200,7 +26200,7 @@
       </c>
       <c r="P334" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q334" s="4" t="n"/>
@@ -26277,7 +26277,7 @@
       </c>
       <c r="P335" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q335" s="4" t="n"/>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="P336" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="Q336" s="4" t="n"/>
@@ -26439,7 +26439,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
